--- a/debug/excel_overviews/gpt-4.1_vs_Llama-3.1-8B-Instruct/Llama-3.1-8B-Instruct/metrics_default_vs_simple.xlsx
+++ b/debug/excel_overviews/gpt-4.1_vs_Llama-3.1-8B-Instruct/Llama-3.1-8B-Instruct/metrics_default_vs_simple.xlsx
@@ -420,25 +420,25 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>0.25</v>
+        <v>0.5263157894736842</v>
       </c>
       <c r="B2">
-        <v>0.25</v>
+        <v>0.05555555555555555</v>
       </c>
       <c r="C2">
-        <v>0.4</v>
+        <v>0.5070422535211268</v>
       </c>
       <c r="D2">
-        <v>0.75</v>
+        <v>0.625</v>
       </c>
       <c r="E2">
-        <v>4</v>
+        <v>76</v>
       </c>
       <c r="F2">
-        <v>4</v>
+        <v>36</v>
       </c>
       <c r="G2">
-        <v>2</v>
+        <v>30</v>
       </c>
     </row>
   </sheetData>

--- a/debug/excel_overviews/gpt-4.1_vs_Llama-3.1-8B-Instruct/Llama-3.1-8B-Instruct/metrics_default_vs_simple.xlsx
+++ b/debug/excel_overviews/gpt-4.1_vs_Llama-3.1-8B-Instruct/Llama-3.1-8B-Instruct/metrics_default_vs_simple.xlsx
@@ -420,25 +420,25 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>0.5263157894736842</v>
+        <v>0.4936708860759494</v>
       </c>
       <c r="B2">
-        <v>0.05555555555555555</v>
+        <v>0.05128205128205128</v>
       </c>
       <c r="C2">
-        <v>0.5070422535211268</v>
+        <v>0.45</v>
       </c>
       <c r="D2">
-        <v>0.625</v>
+        <v>0.652542372881356</v>
       </c>
       <c r="E2">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="F2">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="G2">
-        <v>30</v>
+        <v>22</v>
       </c>
     </row>
   </sheetData>
